--- a/property_management_forms/020_room_evaluation_checklist--property_management_forms.xlsx
+++ b/property_management_forms/020_room_evaluation_checklist--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'bad',_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Bad', 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'air_conditioning',_'label':_'air_conditioning'}</t>
+          <t>air_conditioning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Air conditioning', 'label': 'Air conditioning'}</t>
+          <t>Air conditioning</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bathroom_fixtures',_'label':_'bathroom_fixtures'}</t>
+          <t>bathroom_fixtures</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bathroom fixtures', 'label': 'Bathroom fixtures'}</t>
+          <t>Bathroom fixtures</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'electrical',_'label':_'electrical'}</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Electrical', 'label': 'Electrical'}</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'flooring',_'label':_'flooring'}</t>
+          <t>flooring</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Flooring', 'label': 'Flooring'}</t>
+          <t>Flooring</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'painting',_'label':_'painting'}</t>
+          <t>painting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Painting', 'label': 'Painting'}</t>
+          <t>Painting</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'plumbing',_'label':_'plumbing'}</t>
+          <t>plumbing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Plumbing', 'label': 'Plumbing'}</t>
+          <t>Plumbing</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'roofing',_'label':_'roofing'}</t>
+          <t>roofing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Roofing', 'label': 'Roofing'}</t>
+          <t>Roofing</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
